--- a/artfynd/A 45429-2022 artfynd.xlsx
+++ b/artfynd/A 45429-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45429-2022 artfynd.xlsx
+++ b/artfynd/A 45429-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111108763</v>
+        <v>111107408</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505011.1914782</v>
+        <v>505311</v>
       </c>
       <c r="R2" t="n">
-        <v>6897033.514291184</v>
+        <v>6896910</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,40 +743,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,50 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111110795</v>
+        <v>111107442</v>
       </c>
       <c r="B3" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örasjöberget Norr, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505002.7633032479</v>
+        <v>505211</v>
       </c>
       <c r="R3" t="n">
-        <v>6897044.235017529</v>
+        <v>6896936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +844,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -911,53 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111113083</v>
+        <v>111107427</v>
       </c>
       <c r="B4" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Örasjöberget_Norr, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505146.0538440197</v>
+        <v>504988</v>
       </c>
       <c r="R4" t="n">
-        <v>6896859.180777778</v>
+        <v>6897065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,40 +945,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1031,50 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111110681</v>
+        <v>111107443</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504943.3659684632</v>
+        <v>505345</v>
       </c>
       <c r="R5" t="n">
-        <v>6897074.480266967</v>
+        <v>6896911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,19 +1046,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1147,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111110677</v>
+        <v>111107444</v>
       </c>
       <c r="B6" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505168.3738336075</v>
+        <v>505300</v>
       </c>
       <c r="R6" t="n">
-        <v>6896933.41750373</v>
+        <v>6896894</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,19 +1147,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1263,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111109516</v>
+        <v>111109533</v>
       </c>
       <c r="B7" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1303,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505209.9155263496</v>
+        <v>505343</v>
       </c>
       <c r="R7" t="n">
-        <v>6896968.015448831</v>
+        <v>6896905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,19 +1248,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111109272</v>
+        <v>111107118</v>
       </c>
       <c r="B8" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,37 +1292,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505205.3291968547</v>
+        <v>505133</v>
       </c>
       <c r="R8" t="n">
-        <v>6896911.540464748</v>
+        <v>6896883</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,19 +1349,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1495,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111107444</v>
+        <v>111108945</v>
       </c>
       <c r="B9" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,37 +1393,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505300.6992577018</v>
+        <v>505252</v>
       </c>
       <c r="R9" t="n">
-        <v>6896893.955220446</v>
+        <v>6896931</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,39 +1453,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1611,15 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111107414</v>
+        <v>111109518</v>
       </c>
       <c r="B10" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,34 +1498,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505010.6845764672</v>
+        <v>505009</v>
       </c>
       <c r="R10" t="n">
-        <v>6897060.113268752</v>
+        <v>6897051</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,19 +1555,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,12 +1572,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1727,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111107413</v>
+        <v>111113078</v>
       </c>
       <c r="B11" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,34 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505149.2184701476</v>
+        <v>505342</v>
       </c>
       <c r="R11" t="n">
-        <v>6896929.18807634</v>
+        <v>6896920</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,19 +1656,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,12 +1673,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1843,50 +1689,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111107429</v>
+        <v>111143078</v>
       </c>
       <c r="B12" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>2013</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget NV, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505299.8995778976</v>
+        <v>505207</v>
       </c>
       <c r="R12" t="n">
-        <v>6896808.083162693</v>
+        <v>6896912</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,22 +1757,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar på undersidan av hård och bränd tallåga. Tidigare rapporterad som fläckporing, vilket var felaktigt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,18 +1776,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Carl Jansson, Linda Spjut</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1959,15 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111110794</v>
+        <v>111108797</v>
       </c>
       <c r="B13" t="n">
-        <v>106732</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,37 +1825,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220204</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örasjöberget Norr, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505005.1104265744</v>
+        <v>505081</v>
       </c>
       <c r="R13" t="n">
-        <v>6897037.238561251</v>
+        <v>6897027</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2032,39 +1885,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2075,53 +1919,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111110793</v>
+        <v>111109272</v>
       </c>
       <c r="B14" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Örasjöberget Norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505078.1387900012</v>
+        <v>505206</v>
       </c>
       <c r="R14" t="n">
-        <v>6896956.14743948</v>
+        <v>6896912</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2148,19 +1987,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2191,50 +2020,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111107442</v>
+        <v>111113082</v>
       </c>
       <c r="B15" t="n">
-        <v>89646</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505211.3673929375</v>
+        <v>505212</v>
       </c>
       <c r="R15" t="n">
-        <v>6896935.817108292</v>
+        <v>6896937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2264,19 +2088,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,12 +2105,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2307,37 +2121,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111107117</v>
+        <v>111107131</v>
       </c>
       <c r="B16" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2347,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505169.7236493648</v>
+        <v>505087</v>
       </c>
       <c r="R16" t="n">
-        <v>6896967.486873839</v>
+        <v>6896997</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2380,19 +2189,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,37 +2222,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111109531</v>
+        <v>111109280</v>
       </c>
       <c r="B17" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2463,13 +2257,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505067.852716753</v>
+        <v>504935</v>
       </c>
       <c r="R17" t="n">
-        <v>6896958.931999788</v>
+        <v>6897076</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2496,19 +2290,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,12 +2307,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2539,15 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111109530</v>
+        <v>111107125</v>
       </c>
       <c r="B18" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,14 +2354,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505213.668813225</v>
+        <v>505037</v>
       </c>
       <c r="R18" t="n">
-        <v>6896958.687782467</v>
+        <v>6896961</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,19 +2391,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,12 +2408,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2655,15 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111109267</v>
+        <v>111107428</v>
       </c>
       <c r="B19" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,37 +2435,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505048.1188532721</v>
+        <v>505247</v>
       </c>
       <c r="R19" t="n">
-        <v>6897028.902770294</v>
+        <v>6896804</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2728,19 +2492,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,12 +2509,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2771,15 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111108945</v>
+        <v>111107429</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,40 +2536,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505252.0350032499</v>
+        <v>505300</v>
       </c>
       <c r="R20" t="n">
-        <v>6896931.213470625</v>
+        <v>6896808</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2847,40 +2593,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2891,15 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111113081</v>
+        <v>111107439</v>
       </c>
       <c r="B21" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,14 +2657,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Örasjöberget_Norr, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505294.0681506192</v>
+        <v>505346</v>
       </c>
       <c r="R21" t="n">
-        <v>6896949.946316067</v>
+        <v>6896909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,19 +2694,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,12 +2711,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3007,15 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111107408</v>
+        <v>111107440</v>
       </c>
       <c r="B22" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,21 +2738,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3047,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505311.4229301895</v>
+        <v>505041</v>
       </c>
       <c r="R22" t="n">
-        <v>6896910.305978795</v>
+        <v>6897034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3080,19 +2795,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3123,15 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111107428</v>
+        <v>111107441</v>
       </c>
       <c r="B23" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505246.6257610674</v>
+        <v>505011</v>
       </c>
       <c r="R23" t="n">
-        <v>6896803.332844504</v>
+        <v>6897060</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,19 +2896,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,15 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111107420</v>
+        <v>111108954</v>
       </c>
       <c r="B24" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3255,37 +2940,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505313.4218953817</v>
+        <v>505252</v>
       </c>
       <c r="R24" t="n">
-        <v>6896828.172284967</v>
+        <v>6896931</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3312,39 +3000,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3355,15 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111109529</v>
+        <v>111109000</v>
       </c>
       <c r="B25" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,19 +3063,22 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505297.3902796506</v>
+        <v>505375</v>
       </c>
       <c r="R25" t="n">
-        <v>6896917.750776393</v>
+        <v>6896935</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3428,39 +3105,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3471,15 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111109266</v>
+        <v>111109519</v>
       </c>
       <c r="B26" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,21 +3150,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3511,13 +3174,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505253.4618228037</v>
+        <v>505327</v>
       </c>
       <c r="R26" t="n">
-        <v>6896915.348604402</v>
+        <v>6896822</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3544,19 +3207,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,12 +3224,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3587,15 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111107125</v>
+        <v>111109528</v>
       </c>
       <c r="B27" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,14 +3271,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>505037.0029703763</v>
+        <v>505344</v>
       </c>
       <c r="R27" t="n">
-        <v>6896961.685787642</v>
+        <v>6896914</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3660,19 +3308,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3687,12 +3325,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3703,15 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111107440</v>
+        <v>111109529</v>
       </c>
       <c r="B28" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3739,14 +3372,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>505041.1016625602</v>
+        <v>505297</v>
       </c>
       <c r="R28" t="n">
-        <v>6897033.558906036</v>
+        <v>6896918</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3776,19 +3409,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3803,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3819,15 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111107131</v>
+        <v>111109530</v>
       </c>
       <c r="B29" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,34 +3453,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>505087.4239347795</v>
+        <v>505214</v>
       </c>
       <c r="R29" t="n">
-        <v>6896997.228552313</v>
+        <v>6896959</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3892,19 +3510,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,12 +3527,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3935,50 +3543,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111107127</v>
+        <v>111109531</v>
       </c>
       <c r="B30" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504981.8176343538</v>
+        <v>505068</v>
       </c>
       <c r="R30" t="n">
-        <v>6896986.804034236</v>
+        <v>6896959</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4008,19 +3611,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4035,12 +3628,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4051,15 +3644,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111113082</v>
+        <v>111110796</v>
       </c>
       <c r="B31" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4067,34 +3655,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Örasjöberget_Norr, Hls</t>
+          <t>Örasjöberget Norr, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>505212.3006696022</v>
+        <v>505003</v>
       </c>
       <c r="R31" t="n">
-        <v>6896936.751906397</v>
+        <v>6897044</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4126,7 +3714,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4136,7 +3724,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4151,12 +3739,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4167,50 +3755,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111107119</v>
+        <v>111113079</v>
       </c>
       <c r="B32" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>505131.9978931576</v>
+        <v>505323</v>
       </c>
       <c r="R32" t="n">
-        <v>6896882.026973002</v>
+        <v>6896949</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,19 +3823,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4267,12 +3840,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4283,15 +3856,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111110792</v>
+        <v>111113081</v>
       </c>
       <c r="B33" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4299,34 +3867,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Örasjöberget Norr, Hls</t>
+          <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505178.2127873416</v>
+        <v>505294</v>
       </c>
       <c r="R33" t="n">
-        <v>6896917.56553015</v>
+        <v>6896950</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4356,19 +3924,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4383,12 +3941,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4399,15 +3957,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111113079</v>
+        <v>111113083</v>
       </c>
       <c r="B34" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4433,16 +3986,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505323.0458357625</v>
+        <v>505146</v>
       </c>
       <c r="R34" t="n">
-        <v>6896949.058616129</v>
+        <v>6896859</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4472,27 +4028,18 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4515,15 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111109518</v>
+        <v>111107115</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4531,34 +4073,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>505008.8283847816</v>
+        <v>505203</v>
       </c>
       <c r="R35" t="n">
-        <v>6897051.243955152</v>
+        <v>6896859</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4588,19 +4130,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4615,12 +4147,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4631,50 +4163,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111110682</v>
+        <v>111107116</v>
       </c>
       <c r="B36" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505243.8026079526</v>
+        <v>505072</v>
       </c>
       <c r="R36" t="n">
-        <v>6896815.462516351</v>
+        <v>6896995</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4704,19 +4231,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4731,12 +4248,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4747,15 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111108957</v>
+        <v>111107412</v>
       </c>
       <c r="B37" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4763,40 +4275,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505252.0350032499</v>
+        <v>505203</v>
       </c>
       <c r="R37" t="n">
-        <v>6896931.213470625</v>
+        <v>6896910</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4823,40 +4332,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4867,37 +4365,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111107129</v>
+        <v>111107413</v>
       </c>
       <c r="B38" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4907,10 +4400,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505071.5522396227</v>
+        <v>505149</v>
       </c>
       <c r="R38" t="n">
-        <v>6896985.071215291</v>
+        <v>6896929</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4940,19 +4433,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4967,12 +4450,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4983,15 +4466,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111107121</v>
+        <v>111107414</v>
       </c>
       <c r="B39" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4999,21 +4477,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5023,10 +4501,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505203.0738040954</v>
+        <v>505011</v>
       </c>
       <c r="R39" t="n">
-        <v>6896858.801648073</v>
+        <v>6897060</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5056,19 +4534,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5083,12 +4551,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5099,15 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111107115</v>
+        <v>111108827</v>
       </c>
       <c r="B40" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5133,19 +4596,22 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505203.0738040954</v>
+        <v>505156</v>
       </c>
       <c r="R40" t="n">
-        <v>6896858.801648073</v>
+        <v>6896965</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5172,39 +4638,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5215,15 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111109277</v>
+        <v>111108981</v>
       </c>
       <c r="B41" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5231,37 +4683,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>505009.7568287603</v>
+        <v>505238</v>
       </c>
       <c r="R41" t="n">
-        <v>6897055.445284873</v>
+        <v>6896910</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5288,39 +4743,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5331,15 +4777,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111113068</v>
+        <v>111109266</v>
       </c>
       <c r="B42" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5347,37 +4788,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Örasjöberget_Norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>505192.759282874</v>
+        <v>505253</v>
       </c>
       <c r="R42" t="n">
-        <v>6896879.78663288</v>
+        <v>6896916</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5404,19 +4845,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5431,12 +4862,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5447,15 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111110796</v>
+        <v>111109267</v>
       </c>
       <c r="B43" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,37 +4889,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Örasjöberget Norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505002.7633032479</v>
+        <v>505048</v>
       </c>
       <c r="R43" t="n">
-        <v>6897044.235017529</v>
+        <v>6897029</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5520,19 +4946,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5547,12 +4963,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5563,15 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111107123</v>
+        <v>111110795</v>
       </c>
       <c r="B44" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5579,34 +4990,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget Norr, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505069.6736987298</v>
+        <v>505003</v>
       </c>
       <c r="R44" t="n">
-        <v>6896991.135099629</v>
+        <v>6897044</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5638,7 +5049,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5648,7 +5059,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5663,12 +5074,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5679,37 +5090,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111107128</v>
+        <v>111107119</v>
       </c>
       <c r="B45" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5719,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505227.4205264029</v>
+        <v>505132</v>
       </c>
       <c r="R45" t="n">
-        <v>6896830.837931287</v>
+        <v>6896882</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5752,19 +5158,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5795,53 +5191,51 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111107427</v>
+        <v>111108763</v>
       </c>
       <c r="B46" t="n">
-        <v>89768</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>298</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504987.777173617</v>
+        <v>505011</v>
       </c>
       <c r="R46" t="n">
-        <v>6897065.212539406</v>
+        <v>6897033</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5868,39 +5262,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5911,15 +5296,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111110791</v>
+        <v>111109277</v>
       </c>
       <c r="B47" t="n">
-        <v>40905</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5927,37 +5307,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>215713</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Örasjöberget Norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505214.182385932</v>
+        <v>505010</v>
       </c>
       <c r="R47" t="n">
-        <v>6896928.821295046</v>
+        <v>6897055</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5984,19 +5364,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6011,12 +5381,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6027,15 +5397,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111113078</v>
+        <v>111109278</v>
       </c>
       <c r="B48" t="n">
-        <v>79444</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6043,37 +5408,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Örasjöberget_Norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505341.3179352783</v>
+        <v>504925</v>
       </c>
       <c r="R48" t="n">
-        <v>6896920.620197865</v>
+        <v>6897107</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6100,19 +5465,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6127,12 +5482,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Amanda Wiberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6143,15 +5498,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111108797</v>
+        <v>111110680</v>
       </c>
       <c r="B49" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6159,40 +5509,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505080.8359769633</v>
+        <v>504946</v>
       </c>
       <c r="R49" t="n">
-        <v>6897027.085285815</v>
+        <v>6897072</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6219,40 +5566,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6263,56 +5599,60 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111108844</v>
+        <v>111111027</v>
       </c>
       <c r="B50" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505159.9141798123</v>
+        <v>505345</v>
       </c>
       <c r="R50" t="n">
-        <v>6896964.205125996</v>
+        <v>6896928</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6339,40 +5679,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Susanna Larsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Susanna Larsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6383,56 +5712,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111108981</v>
+        <v>111113065</v>
       </c>
       <c r="B51" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>505238.5141860064</v>
+        <v>504977</v>
       </c>
       <c r="R51" t="n">
-        <v>6896910.191847591</v>
+        <v>6897032</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6459,40 +5780,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6503,15 +5813,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111108827</v>
+        <v>111107117</v>
       </c>
       <c r="B52" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6519,40 +5824,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>505155.7065454677</v>
+        <v>505170</v>
       </c>
       <c r="R52" t="n">
-        <v>6896965.132032262</v>
+        <v>6896967</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6579,40 +5881,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6623,15 +5914,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111109517</v>
+        <v>111110677</v>
       </c>
       <c r="B53" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6639,21 +5925,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6663,10 +5949,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>505071.1600336027</v>
+        <v>505168</v>
       </c>
       <c r="R53" t="n">
-        <v>6896935.136511707</v>
+        <v>6896933</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6696,19 +5982,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6728,7 +6004,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6739,50 +6015,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111107412</v>
+        <v>111113084</v>
       </c>
       <c r="B54" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>208249</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>505203.4626251543</v>
+        <v>504942</v>
       </c>
       <c r="R54" t="n">
-        <v>6896909.670858489</v>
+        <v>6897059</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6812,19 +6083,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6839,12 +6100,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6855,15 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111109276</v>
+        <v>111110784</v>
       </c>
       <c r="B55" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41601</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6871,37 +6127,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>215713</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget Norr, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>505182.4499139997</v>
+        <v>504955</v>
       </c>
       <c r="R55" t="n">
-        <v>6896897.50474944</v>
+        <v>6897040</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6930,7 +6186,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6940,7 +6196,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6955,12 +6211,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Amanda Wiberg</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6971,15 +6227,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>111107441</v>
+        <v>111110785</v>
       </c>
       <c r="B56" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41601</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6987,34 +6238,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>215713</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget Norr, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>505010.6845764672</v>
+        <v>505191</v>
       </c>
       <c r="R56" t="n">
-        <v>6897060.113268752</v>
+        <v>6896852</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7046,7 +6297,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7056,7 +6307,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7071,12 +6322,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7090,12 +6341,7 @@
         <v>111110786</v>
       </c>
       <c r="B57" t="n">
-        <v>40905</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41601</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7127,10 +6373,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>505193.2734001093</v>
+        <v>505193</v>
       </c>
       <c r="R57" t="n">
-        <v>6896849.45275719</v>
+        <v>6896850</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7203,50 +6449,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>111113084</v>
+        <v>111110791</v>
       </c>
       <c r="B58" t="n">
-        <v>57580</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41601</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>208249</v>
+        <v>215713</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Örasjöberget_Norr, Hls</t>
+          <t>Örasjöberget Norr, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504941.5185044172</v>
+        <v>505215</v>
       </c>
       <c r="R58" t="n">
-        <v>6897059.544464835</v>
+        <v>6896929</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7278,7 +6519,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7288,7 +6529,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7303,12 +6544,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7319,56 +6560,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111108961</v>
+        <v>111110679</v>
       </c>
       <c r="B59" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>505252.0350032499</v>
+        <v>505244</v>
       </c>
       <c r="R59" t="n">
-        <v>6896931.213470625</v>
+        <v>6896819</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7395,40 +6628,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7439,15 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111110784</v>
+        <v>111110794</v>
       </c>
       <c r="B60" t="n">
-        <v>40905</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7455,21 +6672,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>215713</v>
+        <v>220204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7479,10 +6696,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504955.0995880328</v>
+        <v>505005</v>
       </c>
       <c r="R60" t="n">
-        <v>6897040.431288195</v>
+        <v>6897037</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7514,7 +6731,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7524,7 +6741,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7555,50 +6772,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>111110680</v>
+        <v>111107127</v>
       </c>
       <c r="B61" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504946.6400954038</v>
+        <v>504982</v>
       </c>
       <c r="R61" t="n">
-        <v>6897072.618439047</v>
+        <v>6896987</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7628,19 +6840,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7655,12 +6857,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7671,50 +6873,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>111110679</v>
+        <v>111107128</v>
       </c>
       <c r="B62" t="n">
-        <v>96381</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Örasjöberget N, Hls</t>
+          <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>505243.7967982134</v>
+        <v>505228</v>
       </c>
       <c r="R62" t="n">
-        <v>6896819.196057346</v>
+        <v>6896831</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7744,19 +6941,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7771,12 +6958,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7787,37 +6974,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>111107116</v>
+        <v>111107129</v>
       </c>
       <c r="B63" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7827,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>505072.4721938065</v>
+        <v>505071</v>
       </c>
       <c r="R63" t="n">
-        <v>6896994.872666492</v>
+        <v>6896985</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7860,19 +7042,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7903,56 +7075,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>111108954</v>
+        <v>111107130</v>
       </c>
       <c r="B64" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Örasjöberget norr, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>505252.0350032499</v>
+        <v>504923</v>
       </c>
       <c r="R64" t="n">
-        <v>6896931.213470625</v>
+        <v>6897106</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7979,40 +7143,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -8023,50 +7176,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>111107118</v>
+        <v>111110681</v>
       </c>
       <c r="B65" t="n">
-        <v>78481</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>505132.9312067247</v>
+        <v>504944</v>
       </c>
       <c r="R65" t="n">
-        <v>6896882.96176393</v>
+        <v>6897074</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8096,19 +7244,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8123,12 +7261,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -8139,50 +7277,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>111107120</v>
+        <v>111110682</v>
       </c>
       <c r="B66" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Örasjöberget norr, Hls</t>
+          <t>Örasjöberget N, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>505037.0029703763</v>
+        <v>505244</v>
       </c>
       <c r="R66" t="n">
-        <v>6896961.685787642</v>
+        <v>6896815</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8212,19 +7345,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8239,12 +7362,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8255,37 +7378,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>111110785</v>
+        <v>111110797</v>
       </c>
       <c r="B67" t="n">
-        <v>40905</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>215713</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8295,10 +7413,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>505191.3988786821</v>
+        <v>504921</v>
       </c>
       <c r="R67" t="n">
-        <v>6896852.716692328</v>
+        <v>6897081</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8330,7 +7448,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8340,7 +7458,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8371,53 +7489,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>111143078</v>
+        <v>111113066</v>
       </c>
       <c r="B68" t="n">
-        <v>90264</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2013</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Örasjöberget NV, Hls</t>
+          <t>Örasjöberget_Norr, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>505207</v>
+        <v>504935</v>
       </c>
       <c r="R68" t="n">
-        <v>6896912</v>
+        <v>6897079</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8444,17 +7554,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar på undersidan av hård och bränd tallåga. Tidigare rapporterad som fläckporing, vilket var felaktigt.</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8463,37 +7568,2314 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Carl Jansson, Linda Spjut</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>111113085</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Örasjöberget_Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>504953</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6897129</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>111114348</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fåssjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>504934</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6897092</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Sofia Lundell</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Sofia Lundell</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>111110793</v>
+      </c>
+      <c r="B71" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Örasjöberget Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>505078</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6896956</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>111110799</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Örasjöberget Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>504916</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6897099</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>111107120</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>505037</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6896961</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>111107121</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>505203</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6896859</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>111107123</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>505069</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6896991</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>111107420</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>505313</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6896828</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>111107426</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>505345</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6896911</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>111108844</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>505160</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6896964</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>111108957</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>505252</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6896931</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>111109003</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>505375</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6896935</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>111109276</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Örasjöberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>505183</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6896897</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Amanda Wiberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Amanda Wiberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>111109515</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Örasjöberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>505344</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6896914</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>111109516</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Örasjöberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>505210</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6896968</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>111109517</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Örasjöberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>505071</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6896935</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>111110792</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Örasjöberget Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>505178</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6896917</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>111113068</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Örasjöberget_Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>505193</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6896880</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>111107416</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>505345</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6896911</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>111108961</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>505252</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6896931</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>111110789</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Örasjöberget Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>505339</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6896913</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>111110790</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Örasjöberget Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>505338</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6896910</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>

--- a/artfynd/A 45429-2022 artfynd.xlsx
+++ b/artfynd/A 45429-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107443</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107444</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109533</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107118</t>
         </is>
       </c>
     </row>
@@ -1484,6 +1524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108945</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109518</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113078</t>
         </is>
       </c>
     </row>
@@ -1811,6 +1866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111143078</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108797</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109272</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2118,6 +2188,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113082</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107131</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109280</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107125</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2522,6 +2612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107428</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107429</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2724,6 +2824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107439</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2825,6 +2930,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107440</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2924,6 +3034,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107441</t>
         </is>
       </c>
     </row>
@@ -3031,6 +3146,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108954</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3136,6 +3256,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109000</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3237,6 +3362,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109519</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3338,6 +3468,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109528</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3439,6 +3574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109529</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3540,6 +3680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109530</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3641,6 +3786,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109531</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3752,6 +3902,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110796</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3853,6 +4008,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113079</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3952,6 +4112,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113081</t>
         </is>
       </c>
     </row>
@@ -4059,6 +4224,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113083</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4160,6 +4330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107115</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4261,6 +4436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107116</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4362,6 +4542,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107412</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4463,6 +4648,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107413</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4562,6 +4752,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107414</t>
         </is>
       </c>
     </row>
@@ -4669,6 +4864,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108827</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4774,6 +4974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108981</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4875,6 +5080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109266</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4976,6 +5186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109267</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5087,6 +5302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110795</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5186,6 +5406,11 @@
       <c r="AY45" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107119</t>
         </is>
       </c>
     </row>
@@ -5293,6 +5518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108763</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5394,6 +5624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109277</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5495,6 +5730,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109278</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5596,6 +5836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110680</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5709,6 +5954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111111027</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5810,6 +6060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113065</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5911,6 +6166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107117</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6012,6 +6272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110677</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6113,6 +6378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113084</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6224,6 +6494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110784</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6335,6 +6610,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110785</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6446,6 +6726,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110786</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6557,6 +6842,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110791</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6658,6 +6948,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110679</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6769,6 +7064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110794</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6870,6 +7170,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107127</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6971,6 +7276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107128</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7072,6 +7382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107129</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7173,6 +7488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107130</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7274,6 +7594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110681</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7375,6 +7700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110682</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7486,6 +7816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110797</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7587,6 +7922,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113066</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7686,6 +8026,11 @@
       <c r="AY69" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113085</t>
         </is>
       </c>
     </row>
@@ -7794,6 +8139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111114348</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7905,6 +8255,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110793</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8016,6 +8371,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110799</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8117,6 +8477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107120</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8218,6 +8583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107121</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8319,6 +8689,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107123</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8420,6 +8795,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107420</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8519,6 +8899,11 @@
       <c r="AY77" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107426</t>
         </is>
       </c>
     </row>
@@ -8626,6 +9011,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108844</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8731,6 +9121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108957</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8836,6 +9231,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109003</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8937,6 +9337,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109276</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9038,6 +9443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109515</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9139,6 +9549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109516</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9240,6 +9655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109517</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9351,6 +9771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110792</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9452,6 +9877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113068</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9551,6 +9981,11 @@
       <c r="AY87" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107416</t>
         </is>
       </c>
     </row>
@@ -9658,6 +10093,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108961</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9769,6 +10209,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110789</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9880,8 +10325,104 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110790</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>